--- a/currentbuild/StructureDefinition-mal-patient.xlsx
+++ b/currentbuild/StructureDefinition-mal-patient.xlsx
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -759,7 +759,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -859,7 +859,7 @@
     <t>Patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1655,7 +1655,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1784,7 +1784,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>NK1-7, NK1-3</t>
@@ -2041,7 +2041,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -2389,15 +2389,15 @@
   <dimension ref="A1:AO118"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.03125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.23828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.46484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.49609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2408,27 +2408,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="156.828125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="40.8125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="56.17578125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="134.453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="34.98828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="48.16015625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="34.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11462,7 +11462,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11799,7 +11799,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>443</v>
       </c>
@@ -16267,12 +16267,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO118">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
